--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G105"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pyspark Developer</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82f91b9a65887ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9b63e4891d06d760</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b63e4891d06d760</t>
+          <t>https://www.indeed.com/viewjob?jk=c568f2158282b6b6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Hybrid, Houston based)</t>
+          <t>Senior Java Full Stack React JS Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CSW Industrials</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53bfcfec62e19f29</t>
+          <t>https://www.indeed.com/viewjob?jk=0649029a69d1d2a1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Infrastructure Administrator</t>
+          <t>Senior Java Full Stack React JS Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cefedbcaa538cf57</t>
+          <t>https://www.indeed.com/viewjob?jk=edf4fcd75c4cabd0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c568f2158282b6b6</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SNS, IAM, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, Databricks, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62196b8dbe66970e</t>
+          <t>https://www.indeed.com/viewjob?jk=1140218fae3fb0d5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack React JS Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0649029a69d1d2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack React JS Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,102 +811,102 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf4fcd75c4cabd0</t>
+          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Bhuvi IT Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1140218fae3fb0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
+          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Virtualan Software</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,137 +951,137 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf961188cdaacb2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sakata Seed America</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Woodland, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1e7d9e5049677eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sakata Seed America</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Burlington, WA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Dataflow, Spark, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85a5637990f1a7b</t>
+          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bhuvi IT Solutions</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
+          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Virtualan Software</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,59 +1161,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf961188cdaacb2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Consultant - Data &amp; AI Solutions</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Spark, Snowflake, Databricks Lakehouse, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=372415265e34d8ed</t>
+          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>System Engineer - Automation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Data Engineer-Databricks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>System Engineer - Automation</t>
+          <t>FullStack Engineer (AWS AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+          <t>https://www.indeed.com/viewjob?jk=bfeac083f625981a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Databricks</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,67 +1826,67 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
+          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FullStack Engineer (AWS AI)</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Site Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfeac083f625981a</t>
+          <t>https://www.indeed.com/viewjob?jk=c49ace417083d1b7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Full Stack Web Developer (Junior–Mid)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Expert with Data Engineer</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Dataflow, Spark, PySpark, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4a226f53d4c7a4f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0258502fd0ff63</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AWS Platform Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, ECS, IAM, RDS, Azure, Scala, Snowflake</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa20e78aa361630b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Financial Systems Analyst</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Polar Semiconductor</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,129 +2071,129 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23d719ff138e1d</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
+          <t>https://www.indeed.com/viewjob?jk=ae380943be2d74d9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c5023af7cec558f8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Site Technologies</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49ace417083d1b7</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0258502fd0ff63</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,137 +2281,137 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae380943be2d74d9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Azure Databrick with Anaplan</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>spire</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=855e7c38ba45b423</t>
+          <t>https://www.indeed.com/viewjob?jk=89801ccb77279e9e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
+          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5023af7cec558f8</t>
+          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>CSafe Global</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Monroe, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Platform Services SMTS</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, API Gateway, RDS, GCP, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77306632aba3d62a</t>
+          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer II - Big Data &amp; AWS</t>
+          <t>VDH Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dexter Systems Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2100868d24cad</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9f08ad500594a0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Associate Data Engineer- GCP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=f4a31dee92110efa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89801ccb77279e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19fe0e24c9417c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr. QA Analyst</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
+          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
         </is>
       </c>
     </row>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CSafe Global</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Monroe, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,182 +2761,182 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3bb69b56a9898d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VDH Oracle OCI Cloud Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9f08ad500594a0</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a31dee92110efa</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Integration Engineer</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, SQS, SNS, API Gateway, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c04f106fe6e2d145</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Integration Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Commerce</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, SQS, SNS, API Gateway, Scala, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=101d501682b81b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Architect</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Misch Group</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>IAM, RDS, Scala, Data Modeling, CI/CD, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16bc903fb906c0bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. QA Analyst</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,59 +3086,59 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Senior Full Stack Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3bb69b56a9898d</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>TDS Global Solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,102 +3226,102 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Engineering Data Analytics</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, Athena, S3, RDS, Databricks, Spark, Scala, Fact Tables</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=391a7c687426739b</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Databricks Developer, SAP S/4 Data Products and Governance</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee20fa8ee7d3e166</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (contract)</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>TDS Global Solutions</t>
+          <t>RUSSELL INVESTMENTS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,102 +3366,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
+          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50a380c35ffe71f3</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer</t>
+          <t>Data Engineer / API Integration Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>The McPherson Companies, Inc</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Trussville, AL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Snowflake Schema, Power BI</t>
+          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f03558ae01650be1</t>
+          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Supply Chain Business Analyst</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Dimensional Modeling, ETL, ELT, Power BI, Python</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f19070dba73bb1c5</t>
+          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Scientist with strong Algorithm experience</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, MLOps, CI/CD, Docker, Python, SQL</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6714d23df870368</t>
+          <t>https://www.indeed.com/viewjob?jk=1a875401eb258187</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Developer - IT</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, NoSQL, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=74d1ed54fce13fb1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RUSSELL INVESTMENTS</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer / API Integration Developer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>The McPherson Companies, Inc</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Trussville, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e2d662db85631</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4f84010a2ac741</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,252 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a875401eb258187</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Technuf LLC</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Suitland, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Information Technology Development Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>L.A. Care Health Plan</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Developer II</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Textron</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e2d662db85631</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4f84010a2ac741</t>
+          <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,17 +731,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Databricks, GCP, BigQuery, Cloud Storage, Scala, Snowflake, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1140218fae3fb0d5</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
+          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
+          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bhuvi IT Solutions</t>
+          <t>Virtualan Software</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf961188cdaacb2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Bhuvi IT Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
+          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Virtualan Software</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf961188cdaacb2</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
+          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Engineer - Automation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>System Engineer - Automation</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior Data Engineer-Databricks</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Databricks</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FullStack Engineer (AWS AI)</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfeac083f625981a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Site Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,77 +1816,77 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
+          <t>https://www.indeed.com/viewjob?jk=c49ace417083d1b7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Full Stack Web Developer (Junior–Mid)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Site Technologies</t>
+          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49ace417083d1b7</t>
+          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>Spire Global</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0258502fd0ff63</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0258502fd0ff63</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae380943be2d74d9</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae380943be2d74d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,29 +2131,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5023af7cec558f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>spire</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=89801ccb77279e9e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>CSafe Global</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Monroe, OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89801ccb77279e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>VDH Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dexter Systems Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9f08ad500594a0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CSafe Global</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Monroe, OH, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VDH Oracle OCI Cloud Engineer</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9f08ad500594a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate Data Engineer- GCP</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4a31dee92110efa</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=7c3bb69b56a9898d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Sr. QA Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,164 +2631,164 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. QA Analyst</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3bb69b56a9898d</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Senior Full Stack Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>TDS Global Solutions</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (contract)</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TDS Global Solutions</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Data Engineer / API Integration Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>The McPherson Companies, Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Trussville, AL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RUSSELL INVESTMENTS</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
+          <t>https://www.indeed.com/viewjob?jk=1a875401eb258187</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer / API Integration Developer</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The McPherson Companies, Inc</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Trussville, AL, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Developer - IT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, NoSQL, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
+          <t>https://www.indeed.com/viewjob?jk=74d1ed54fce13fb1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e2d662db85631</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a875401eb258187</t>
+          <t>https://www.indeed.com/viewjob?jk=ab4f84010a2ac741</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Technuf LLC</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Developer - IT</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, NoSQL, Git, CloudWatch</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d1ed54fce13fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Information Technology Development Operations Engineer II</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3680,181 +3680,6 @@
         </is>
       </c>
       <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Developer II</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Textron</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e2d662db85631</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4f84010a2ac741</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
+          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
+          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Virtualan Software</t>
+          <t>Bhuvi IT Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf961188cdaacb2</t>
+          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bhuvi IT Solutions</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
+          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Virtualan Software</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf961188cdaacb2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>System Engineer - Automation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>System Engineer - Automation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Databricks</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer-Databricks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
+          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Site Technologies</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, PostgreSQL, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c49ace417083d1b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Web Developer (Junior–Mid)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
+          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Spire Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Databricks, Spark, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0258502fd0ff63</t>
+          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Snowflake, MySQL, Data Modeling, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae380943be2d74d9</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Software Engineer - RFGL Systems</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>spire</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=89801ccb77279e9e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89801ccb77279e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CSafe Global</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Monroe, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
+          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CSafe Global</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Monroe, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,19 +2351,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
+          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>VDH Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Dexter Systems Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9f08ad500594a0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>VDH Oracle OCI Cloud Engineer</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9f08ad500594a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. QA Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,84 +2561,84 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI Solutions</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c3bb69b56a9898d</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. QA Analyst</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Technuf LLC</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Developer - IT</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, NoSQL, Git, CloudWatch</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d1ed54fce13fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Salesforce Data Cloud Architect</t>
+          <t>Senior Developer - IT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, NoSQL, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e2d662db85631</t>
+          <t>https://www.indeed.com/viewjob?jk=74d1ed54fce13fb1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Salesforce Data Cloud Architect</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4f84010a2ac741</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Broadcast Reliability Engineer</t>
+          <t>Senior Salesforce Data Cloud Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fox Corporation</t>
+          <t>EPAM Systems</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,42 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8a4e2d662db85631</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Data Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab4f84010a2ac741</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bhuvi IT Solutions</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
+          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Bhuvi IT Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
+          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Virtualan Software</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf961188cdaacb2</t>
+          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Warehouse Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Virtualan Software</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=7cf961188cdaacb2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>System Engineer - Automation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>System Engineer - Automation</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Databricks</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer-Databricks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
+          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
+          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Web Developer (Junior–Mid)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - RFGL Systems</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>spire</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Databricks, Spark, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89801ccb77279e9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CSafe Global</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monroe, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
+          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>VDH Oracle OCI Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>CSafe Global</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Monroe, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9f08ad500594a0</t>
+          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>VDH Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Dexter Systems Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=2f9f08ad500594a0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. QA Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,84 +2561,84 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. QA Analyst</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
@@ -2953,17 +2953,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (contract)</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TDS Global Solutions</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,29 +3006,29 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Full Stack Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3037,11 +3037,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>TDS Global Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer / API Integration Developer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The McPherson Companies, Inc</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Trussville, AL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer / API Integration Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>The McPherson Companies, Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Trussville, AL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
+          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a875401eb258187</t>
+          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
+          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
+          <t>https://www.indeed.com/viewjob?jk=1a875401eb258187</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Developer - IT</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, NoSQL, Git, CloudWatch</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d1ed54fce13fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Technuf LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Information Technology Development Operations Engineer II</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Salesforce Data Cloud Architect</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EPAM Systems</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e2d662db85631</t>
+          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
         </is>
       </c>
     </row>
@@ -3715,6 +3715,41 @@
         </is>
       </c>
       <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a4e2d662db85631</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Salesforce Data Cloud Architect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EPAM Systems</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ab4f84010a2ac741</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Full Stack Web Developer (Junior–Mid)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. QA Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Sr. QA Analyst</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,24 +2691,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
@@ -3682,76 +3682,6 @@
       <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Senior Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4e2d662db85631</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Salesforce Data Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>EPAM Systems</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ab4f84010a2ac741</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
@@ -1798,17 +1798,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
@@ -1938,17 +1938,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Web Developer (Junior–Mid)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
+          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,24 +2691,24 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
@@ -3093,17 +3093,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer / API Integration Developer</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>The McPherson Companies, Inc</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Trussville, AL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer / API Integration Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>The McPherson Companies, Inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Trussville, AL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
+          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
+          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a875401eb258187</t>
+          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,25 +958,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Warehouse Architect</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Virtualan Software</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cf961188cdaacb2</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
+          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Engineer - Automation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>System Engineer - Automation</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior Data Engineer-Databricks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1637,11 +1637,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Databricks</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Web Developer (Junior–Mid)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bbc3e06adaa2abd</t>
+          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
@@ -2113,12 +2113,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>CSafe Global</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Monroe, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
+          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CSafe Global</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Monroe, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>VDH Oracle OCI Cloud Engineer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dexter Systems Inc</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f9f08ad500594a0</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Sr. QA Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,112 +2526,112 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. QA Analyst</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Senior Full Stack Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>TDS Global Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,112 +2971,112 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (contract)</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>TDS Global Solutions</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>RUSSELL INVESTMENTS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Engineer / API Integration Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>The McPherson Companies, Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Trussville, AL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer / API Integration Developer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The McPherson Companies, Inc</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trussville, AL, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Technuf LLC</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Information Technology Development Operations Engineer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,42 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
+          <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e3e46ee8cd3dca</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Apollo Technology Solutions LLC</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=417e45e2898523c2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. QA Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Verisk</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Woburn, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,49 +2491,49 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. QA Analyst</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Sr. AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Restaurant Brands International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,17 +2796,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Senior Full Stack Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (contract)</t>
+          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>TDS Global Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TDS Global Solutions</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>RUSSELL INVESTMENTS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RUSSELL INVESTMENTS</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
+          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Data Engineer / API Integration Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>The McPherson Companies, Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Trussville, AL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer / API Integration Developer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The McPherson Companies, Inc</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Trussville, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chantilly, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
+          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,24 +3356,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Technuf LLC</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Information Technology Development Operations Engineer II</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
+          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Aivra Health</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3610,41 +3610,6 @@
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AWS Data Engineer-Cloud Data Engineer</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IPolarity LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60269398d79f897f</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8567ad208bdc93</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8567ad208bdc93</t>
+          <t>https://www.indeed.com/viewjob?jk=9b63e4891d06d760</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b63e4891d06d760</t>
+          <t>https://www.indeed.com/viewjob?jk=c568f2158282b6b6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Senior Java Full Stack React JS Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c568f2158282b6b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0649029a69d1d2a1</t>
         </is>
       </c>
     </row>
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0649029a69d1d2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=edf4fcd75c4cabd0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack React JS Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf4fcd75c4cabd0</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
+          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
         </is>
       </c>
     </row>
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
+          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Bhuvi IT Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bhuvi IT Solutions</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
+          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
+          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Engineer - Automation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>System Engineer - Automation</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior Data Engineer-Databricks</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>EXL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Databricks</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,17 +1641,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CSafe Global</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monroe, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16156455b2efb342</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,84 +2421,84 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. QA Analyst</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Verisk</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=accd204a168b9099</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. AI Enablement Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Restaurant Brands International</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Snowflake, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4e4b82078b11e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Full Stack Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>TDS Global Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,42 +2831,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (contract)</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TDS Global Solutions</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>RUSSELL INVESTMENTS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Engineer / API Integration Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>The McPherson Companies, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Trussville, AL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RUSSELL INVESTMENTS</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer / API Integration Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>The McPherson Companies, Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Trussville, AL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dedb843e72fa5a35</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07c53e098cdc93c</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
+          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3435,181 +3435,6 @@
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Technuf LLC</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Suitland, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Information Technology Development Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>L.A. Care Health Plan</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Developer II</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Textron</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Senior Java Full Stack React JS Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c568f2158282b6b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0649029a69d1d2a1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack React JS Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0649029a69d1d2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack React JS Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edf4fcd75c4cabd0</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
+          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
+          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Bhuvi IT Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bhuvi IT Solutions</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>DICK'S Sporting Goods</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
+          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
+          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>System Engineer - Automation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Moxie Pest Control</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>System Engineer - Automation</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,77 +1501,77 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-Databricks</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EXL</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d62bcdf946e0e2c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,77 +1746,77 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>Full Stack Web Developer (Junior–Mid)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,19 +2211,19 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,112 +2316,112 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Senior Full Stack Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (contract)</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Customer Experience (CX) Technology, Engineering &amp; Product Professionals</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TDS Global Solutions</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, GCP, Snowflake, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6599b1124e4e45f</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>RUSSELL INVESTMENTS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RUSSELL INVESTMENTS</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer / API Integration Developer</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The McPherson Companies, Inc</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Trussville, AL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=971c85159c133be2</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,225 +3216,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Technuf LLC</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Suitland, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Information Technology Development Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>L.A. Care Health Plan</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Developer II</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Textron</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Junior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Aivra Health</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, SQL Server, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=651e0dbd42a31f53</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Bhuvi IT Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
+          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bhuvi IT Solutions</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
+          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
         </is>
       </c>
     </row>
@@ -1308,17 +1308,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer 2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>CPS Energy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>Pantherx Specialty Llc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Full Stack Web Developer (Junior–Mid)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
@@ -2078,25 +2078,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca8d0f916325965c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ffb9a704d3643de</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
@@ -2288,25 +2288,25 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Supply Chain Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,24 +2341,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Senior Full Stack Software Engineer (contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (contract)</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Data Platform Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>RUSSELL INVESTMENTS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Platform Engineer II</t>
+          <t>Data Collection Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RUSSELL INVESTMENTS</t>
+          <t>Two Six Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
+          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Collection Engineer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Two Six Technologies</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Technuf LLC</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Information Technology Development Operations Engineer II</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>L.A. Care Health Plan</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Developer II</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Textron</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3190,41 +3190,6 @@
         </is>
       </c>
       <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Medallion Architecture, Spark</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=248b5eaae24b8d28</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DICK'S Sporting Goods</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Spark, PySpark, Snowflake</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a7217a792dd5e03</t>
+          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,102 +1371,102 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer 2</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CPS Energy</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Dataflow, Hadoop, Hive, MapReduce, HBase, Spark, Kafka, Informatica PowerCenter</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f75dbc2c4d33da8c</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>System Engineer - Automation</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Moxie Pest Control</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, BigQuery, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d86659fb0c9981b7</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Senior Software Engineer – Platform Services</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,137 +1651,137 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pantherx Specialty Llc</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31c0459cc1b7e4dd</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=939e008d96e1a463</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer (Junior–Mid)</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AutoIQ - An Imperial Quest, LLC. Company</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, PostgreSQL, MySQL, CI/CD, GitHub Actions, Docker, pytest</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d2f14db96d8d8c</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Java Backend developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,172 +2001,172 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, ETL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40622e5a0a996f23</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,59 +2246,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Supply Chain Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Snowflake, Oracle, ETL, ELT, dbt, DataOps</t>
+          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b45757fcb27c5bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,137 +2386,137 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,137 +2526,137 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (contract)</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, ETL, ELT, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbe5ac9ecb45aa70</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2770,426 +2770,6 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Handshake</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Computer Programmer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Zensar Technologies</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Pacific Life</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Data Platform Engineer II</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>RUSSELL INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, dbt, Power BI, Tableau, Python</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7647430742e0e326</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Data Collection Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Two Six Technologies</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Kafka, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa42b4ae7575796</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Data Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Technuf LLC</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Suitland, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Information Technology Development Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>L.A. Care Health Plan</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Developer II</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Textron</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Senior Data Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Samsara</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Azure, Databricks, Google Cloud Platform, GCP, Hadoop, Hive, HBase</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e8567ad208bdc93</t>
+          <t>https://www.indeed.com/viewjob?jk=9b63e4891d06d760</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer II</t>
+          <t>Senior Java Full Stack React JS Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Samsara</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Azure, Databricks, GCP</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b63e4891d06d760</t>
+          <t>https://www.indeed.com/viewjob?jk=0649029a69d1d2a1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack React JS Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0649029a69d1d2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
         </is>
       </c>
     </row>
@@ -648,20 +648,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
+          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Full Stack Java Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Bhuvi IT Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,77 +731,77 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094b99fc9faf620d</t>
+          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>South College</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bhuvi IT Solutions</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163b6526177b1b3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,102 +916,102 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b476bc965c1527c</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffcf4f82e0373e4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2a96ccd0231a8de</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Software engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24962e9aa692f429</t>
+          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf4bcb7975fa63a</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a71ba248e484044</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c867f808b4a82623</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c1d6a47764425d3</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Information Technology - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Marana Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Marana, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34668af6612803b</t>
+          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5f5f795c564e723</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Platform Services</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, PostgreSQL, MongoDB, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f0a023332a0c5fd</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,242 +1931,242 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Java Backend developer</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Oracle, Cassandra, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a04605f9f4b5ba99</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Technuf LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Suitland, MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Developer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2175,601 +2175,6 @@
         </is>
       </c>
       <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Pacific Life</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Newport Beach, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=285c09e31afcad5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Enterprise Application &amp; Data Architect</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Expleo Group</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Point One Navigation</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Point One Navigation</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Data Engineer II</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Pacific Life</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Spark, Snowflake, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9058e1e39a092453</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-07-11</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>BI Reporting Engineer</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Lifetime Brands</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Garden City, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Handshake</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Handshake</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Computer Programmer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Zensar Technologies</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Data Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Technuf LLC</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Suitland, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Information Technology Development Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>L.A. Care Health Plan</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Developer II</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Textron</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,25 +713,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Java Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bhuvi IT Solutions</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f12eba397b477</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>South College</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec2a4011d2b744c</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native Builder-Europe</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,129 +846,129 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software engineer</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fidelity Investments</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,77 +1011,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, ECS, Scala, Kafka, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7eaaaa4374b1b66</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Information Technology - Senior Data Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Marana Health</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marana, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athena, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521143d7768e20ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer (Platform Core)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>AI Solution Architect - Enterprise Intelligence</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Full-Stack Software Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Brigham Young University</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Provo, UT, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,54 +1336,54 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,108 +1392,108 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,99 +1606,99 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1707,46 +1707,46 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer Intern/Co-op</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,225 +1956,15 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Enterprise Solution Architect - AWS Modernization &amp; Legacy Transformation</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Technuf LLC</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Suitland, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc502578017bc82</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Information Technology Development Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>L.A. Care Health Plan</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Developer II</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Textron</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Providence, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, Kubernetes, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2fd891eedd7d004</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack React JS Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0649029a69d1d2a1</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>RWE</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8e383943021fcf6</t>
+          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
         </is>
       </c>
     </row>
@@ -648,20 +648,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Elevate Aviation Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,54 +671,54 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057c8f8e8ea92f8c</t>
+          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Analytica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Delta Live Tables, Cloud Storage, Scala, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=275b7a8c06aa4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Elevate Aviation Group</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,164 +741,164 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9383db09846c90f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Native Builder-Europe</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=117cf58c0cc74040</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>Analytics Data Engineer (BI/Fabric)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>LifeWave</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer (BI/Fabric)</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LifeWave</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=116ca6571d543788</t>
+          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,102 +1196,102 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Platform Core)</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, S3, IAM, RDS, GCP, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca782c004240a6c</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Solution Architect - Enterprise Intelligence</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, ECS, RDS, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,59 +1301,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3913715bcf2ea8f</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full-Stack Software Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Brigham Young University</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, PostgreSQL, MongoDB, NoSQL, Data Modeling, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=927a1a9e76672e0a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,129 +1511,129 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>Zensar Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Information Technology Development Operations Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>L.A. Care Health Plan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1755,216 +1755,6 @@
         </is>
       </c>
       <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Computer Programmer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Zensar Technologies</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Data Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Information Technology Development Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>L.A. Care Health Plan</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>

--- a/results/job_matches_2026-07-11.xlsx
+++ b/results/job_matches_2026-07-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Sqoop, HBase, Flume, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hive, Spark, Scala, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2f5df91db55ec9</t>
+          <t>https://www.indeed.com/viewjob?jk=adbee2c9c0e985dc</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Analytica</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da635d22afcd5e76</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Architect</t>
+          <t>HR AI/ML Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Airbus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f3cc801c79c8e7</t>
+          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aee672823e50ae6</t>
+          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, Azure, Databricks, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=565b08a71b6647d2</t>
+          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ross Dress For Less</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ross Dress For Less</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Azure Cosmos DB, NoSQL, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c380088294d31182</t>
+          <t>https://www.indeed.com/viewjob?jk=a1d894dc94f127d6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Associate - Full Stack Developer - Wealth Management Technology</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, ECS, RDS, Databricks, Scala</t>
+          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bc74ef26d52ec8e</t>
+          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Solution Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, BigQuery, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a1e14429b49571c</t>
+          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Solution Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Coreforce</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b6f9e26dbe6cc6c</t>
+          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
         </is>
       </c>
     </row>
@@ -1028,25 +1028,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Coreforce</t>
+          <t>Axos Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,84 +1056,84 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9969ce677805a3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d59203a860169de9</t>
+          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML/AI Engineers</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Axos Bank</t>
+          <t>Adidev Technologies Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c60e10a1b6481c3</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Jr - Mid Level Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521e9a8cf4de7cf2</t>
+          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ML/AI Engineers</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab9861ce9c451ec</t>
+          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jr - Mid Level Machine Learning Engineer</t>
+          <t>Full Stack Product Builder</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Michael Baker International</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e63c93a86a5d45e</t>
+          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Enterprise Application &amp; Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adidev Technologies Inc</t>
+          <t>Expleo Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, ELT, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=783b7f98787ded08</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full Stack Product Builder</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Michael Baker International</t>
+          <t>Point One Navigation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3934e1788c4103b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1b105ae72cedfb</t>
+          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer II - Platform Engineer/Databricks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Point One Navigation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894f57d9a1c304cf</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Application &amp; Data Architect</t>
+          <t>BI Reporting Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Expleo Group</t>
+          <t>Lifetime Brands</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Garden City, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Data Modeling, dbt, DataOps, CI/CD, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4e35be75f84fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II - Platform Engineer/Databricks</t>
+          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Handshake</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Jenkins, Maven, Terraform, Jenkins, Git</t>
+          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e6a9633dc466a51</t>
+          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BI Reporting Engineer</t>
+          <t>Data Engineer Intern/Co-op</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lifetime Brands</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Garden City, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c21b9e62ae83831d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Senior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c5f1eb5fe027fb0</t>
+          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Handshake</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c03ea918065ec279</t>
+          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Broadcast Reliability Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zensar Technologies</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1580,181 +1580,6 @@
         </is>
       </c>
       <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2f7b6f75590ec5d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Engineer Intern/Co-op</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Step Functions, S3, RDS, Scala, SQL Server, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2bafe231fd54f8af</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Senior AWS Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Plymouth Rock Assurance</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-04-17</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1641a10b9bb89296</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c55ccf18cdc7f7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Information Technology Development Operations Engineer II</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>L.A. Care Health Plan</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b16ef14984de3ac1</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Senior Broadcast Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Fox Corporation</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Tempe, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=98d6ac80c240f5cd</t>
         </is>
